--- a/data/generic_crop.xlsx
+++ b/data/generic_crop.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10719"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidfreebairn/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidfreebairn/Desktop/soilwater-app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF1E7604-2B91-404B-9848-87DF7F9F78D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4188A0A0-A264-CC4B-9B40-FCC12DA52332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="600" windowWidth="36740" windowHeight="18500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -953,28 +953,28 @@
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>40</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>60</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>110</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>120</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>120</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -1884,11 +1884,11 @@
         <v>30</v>
       </c>
       <c r="E15" s="18">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F15" s="19">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G15" s="18">
         <v>12</v>
@@ -1910,11 +1910,11 @@
         <v>30</v>
       </c>
       <c r="E16" s="18">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F16" s="19">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G16" s="18">
         <v>13</v>
@@ -1962,11 +1962,11 @@
         <v>30</v>
       </c>
       <c r="E18" s="18">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="F18" s="19">
         <f t="shared" si="0"/>
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G18" s="18">
         <v>15</v>
@@ -1988,11 +1988,11 @@
         <v>30</v>
       </c>
       <c r="E19" s="18">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F19" s="19">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G19" s="18">
         <v>16</v>
@@ -2014,11 +2014,11 @@
         <v>30</v>
       </c>
       <c r="E20" s="18">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="F20" s="19">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G20" s="18">
         <v>17</v>
@@ -2040,11 +2040,11 @@
         <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="F21" s="19">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G21" s="18">
         <v>18</v>
@@ -2066,11 +2066,11 @@
         <v>30</v>
       </c>
       <c r="E22" s="18">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="F22" s="19">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G22" s="18">
         <v>19</v>
@@ -2223,7 +2223,7 @@
         <v>30</v>
       </c>
       <c r="E28" s="15">
-        <f t="shared" ref="D28:F28" si="3">E4</f>
+        <f t="shared" ref="E28:F28" si="3">E4</f>
         <v>0</v>
       </c>
       <c r="F28" s="15">
